--- a/output/roomself_excel/1237.xlsx
+++ b/output/roomself_excel/1237.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>123188</v>
+        <v>122958</v>
       </c>
       <c r="D2" t="n">
-        <v>2844</v>
+        <v>3211</v>
       </c>
       <c r="E2" t="n">
-        <v>450</v>
+        <v>305</v>
       </c>
       <c r="F2" t="n">
-        <v>335</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>597662</v>
+        <v>369727</v>
       </c>
       <c r="D3" t="n">
-        <v>8976</v>
+        <v>6191</v>
       </c>
       <c r="E3" t="n">
         <v>897</v>
       </c>
       <c r="F3" t="n">
-        <v>819</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29252</v>
+        <v>123188</v>
       </c>
       <c r="D4" t="n">
-        <v>1392</v>
+        <v>2844</v>
       </c>
       <c r="E4" t="n">
-        <v>206</v>
+        <v>450</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32548</v>
+        <v>118256</v>
       </c>
       <c r="D6" t="n">
-        <v>1456</v>
+        <v>2772</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>94879</v>
+        <v>32548</v>
       </c>
       <c r="D7" t="n">
-        <v>2696</v>
+        <v>1456</v>
       </c>
       <c r="E7" t="n">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>118256</v>
+        <v>49680</v>
       </c>
       <c r="D8" t="n">
-        <v>2772</v>
+        <v>1788</v>
       </c>
       <c r="E8" t="n">
-        <v>304</v>
+        <v>207</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22448</v>
+        <v>104977</v>
       </c>
       <c r="D9" t="n">
-        <v>1224</v>
+        <v>2872</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>206</v>
       </c>
       <c r="F9" t="n">
         <v>38</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49680</v>
+        <v>29252</v>
       </c>
       <c r="D10" t="n">
-        <v>1788</v>
+        <v>1392</v>
       </c>
       <c r="E10" t="n">
-        <v>440</v>
+        <v>206</v>
       </c>
       <c r="F10" t="n">
-        <v>223</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -668,15 +668,59 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>94879</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2696</v>
+      </c>
+      <c r="E11" t="n">
+        <v>195</v>
+      </c>
+      <c r="F11" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>22448</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E12" t="n">
+        <v>122</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>32016</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>1432</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" t="n">
         <v>222</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F13" t="n">
         <v>212</v>
       </c>
     </row>

--- a/output/roomself_excel/1237.xlsx
+++ b/output/roomself_excel/1237.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3211</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>305</v>
       </c>
-      <c r="F2" t="n">
-        <v>38</v>
-      </c>
+      <c r="G2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>6191</v>
       </c>
-      <c r="E3" t="n">
-        <v>897</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>602</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>297</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2844</v>
       </c>
-      <c r="E4" t="n">
-        <v>450</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>335</v>
+        <v>412</v>
+      </c>
+      <c r="G4" t="n">
+        <v>36</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>299</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +601,26 @@
       <c r="D5" t="n">
         <v>2908</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>304</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>423</v>
+      </c>
+      <c r="J5" t="n">
         <v>36</v>
       </c>
     </row>
@@ -563,10 +639,26 @@
       <c r="D6" t="n">
         <v>2772</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>389</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>304</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -585,12 +677,12 @@
       <c r="D7" t="n">
         <v>1456</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1788</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>207</v>
       </c>
-      <c r="F8" t="n">
-        <v>38</v>
-      </c>
+      <c r="G8" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>2872</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>206</v>
       </c>
-      <c r="F9" t="n">
-        <v>38</v>
-      </c>
+      <c r="G9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>1392</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>206</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>36</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +789,20 @@
       <c r="D11" t="n">
         <v>2696</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>195</v>
       </c>
-      <c r="F11" t="n">
-        <v>38</v>
-      </c>
+      <c r="G11" t="n">
+        <v>38</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +819,20 @@
       <c r="D12" t="n">
         <v>1224</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>122</v>
       </c>
-      <c r="F12" t="n">
-        <v>38</v>
-      </c>
+      <c r="G12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,11 +849,27 @@
       <c r="D13" t="n">
         <v>1432</v>
       </c>
-      <c r="E13" t="n">
-        <v>222</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>212</v>
+        <v>174</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>184</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1237.xlsx
+++ b/output/roomself_excel/1237.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,66 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +569,30 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>60</v>
+      </c>
+      <c r="N2" t="n">
+        <v>38</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -547,6 +631,54 @@
       <c r="J3" t="n">
         <v>38</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>244</v>
+      </c>
+      <c r="N3" t="n">
+        <v>36</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>87</v>
+      </c>
+      <c r="R3" t="n">
+        <v>36</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>242</v>
+      </c>
+      <c r="V3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,6 +717,30 @@
       <c r="J4" t="n">
         <v>38</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>185</v>
+      </c>
+      <c r="N4" t="n">
+        <v>36</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -623,6 +779,42 @@
       <c r="J5" t="n">
         <v>36</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>184</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="n">
+        <v>36</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -661,6 +853,42 @@
       <c r="J6" t="n">
         <v>38</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>59</v>
+      </c>
+      <c r="N6" t="n">
+        <v>36</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>122</v>
+      </c>
+      <c r="R6" t="n">
+        <v>38</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -683,6 +911,18 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -713,6 +953,30 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>59</v>
+      </c>
+      <c r="N8" t="n">
+        <v>38</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -743,6 +1007,30 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>97</v>
+      </c>
+      <c r="N9" t="n">
+        <v>38</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -773,6 +1061,18 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -803,6 +1103,30 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>85</v>
+      </c>
+      <c r="N11" t="n">
+        <v>38</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -833,6 +1157,30 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>87</v>
+      </c>
+      <c r="N12" t="n">
+        <v>38</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -871,6 +1219,30 @@
       <c r="J13" t="n">
         <v>38</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>59</v>
+      </c>
+      <c r="N13" t="n">
+        <v>38</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
